--- a/public/docs/planilla-modelo-altaMasiva.xlsx
+++ b/public/docs/planilla-modelo-altaMasiva.xlsx
@@ -1,13 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\farme\OneDrive\Escritorio\Farmerin\Planillas Alta y Atc - New\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D450133-5C10-4323-8F33-4E4F5FEFCB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Hoja 1" sheetId="1" r:id="rId4"/>
+    <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="1NvOwDrarsTTrB0tfN9ol3P+v8qrddkWmPYaffSTWfA="/>
     </ext>
@@ -16,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="71">
   <si>
     <t>eRP (boton)</t>
   </si>
@@ -226,45 +238,50 @@
   </si>
   <si>
     <t>G4228</t>
+  </si>
+  <si>
+    <t>Grupo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy&quot;/&quot;mm&quot;/&quot;dd&quot;/&quot;"/>
     <numFmt numFmtId="165" formatCode="yyyy&quot;/&quot;m&quot;/&quot;d&quot;/&quot;"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -274,7 +291,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -284,7 +301,13 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -298,65 +321,69 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="15">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="165" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="4" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -546,32 +573,35 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:Z1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.75"/>
-    <col customWidth="1" min="2" max="2" width="12.13"/>
-    <col customWidth="1" min="3" max="3" width="24.0"/>
-    <col customWidth="1" min="4" max="4" width="9.63"/>
-    <col customWidth="1" min="5" max="5" width="8.63"/>
-    <col customWidth="1" min="6" max="6" width="15.75"/>
-    <col customWidth="1" min="7" max="7" width="24.63"/>
-    <col customWidth="1" min="8" max="8" width="9.25"/>
-    <col customWidth="1" min="9" max="9" width="13.88"/>
-    <col customWidth="1" min="10" max="10" width="11.13"/>
-    <col customWidth="1" min="11" max="11" width="17.75"/>
-    <col customWidth="1" min="12" max="12" width="24.38"/>
-    <col customWidth="1" min="13" max="13" width="13.0"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" customWidth="1"/>
+    <col min="7" max="7" width="24.5703125" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.85546875" customWidth="1"/>
+    <col min="10" max="10" width="11.140625" customWidth="1"/>
+    <col min="11" max="11" width="17.7109375" customWidth="1"/>
+    <col min="12" max="12" width="24.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -611,7 +641,9 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4"/>
+      <c r="N1" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
       <c r="Q1" s="4"/>
@@ -625,18 +657,18 @@
       <c r="Y1" s="4"/>
       <c r="Z1" s="4"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
-        <v>9.64E14</v>
+        <v>964000000000000</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D2" s="7">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>14</v>
@@ -645,10 +677,10 @@
         <v>15</v>
       </c>
       <c r="G2" s="8">
-        <v>45144.0</v>
+        <v>45144</v>
       </c>
       <c r="H2" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="I2" s="9">
         <v>13.4</v>
@@ -658,22 +690,25 @@
         <v>16</v>
       </c>
       <c r="L2" s="10">
-        <v>45192.0</v>
+        <v>45192</v>
       </c>
       <c r="M2" s="5"/>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
+      <c r="N2" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
-        <v>9.64000000000001E14</v>
+        <v>964000000000001</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C3" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D3" s="7">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>14</v>
@@ -682,35 +717,38 @@
         <v>15</v>
       </c>
       <c r="G3" s="8">
-        <v>44957.0</v>
+        <v>44957</v>
       </c>
       <c r="H3" s="5">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="I3" s="9">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="J3" s="7"/>
       <c r="K3" s="5" t="s">
         <v>16</v>
       </c>
       <c r="L3" s="10">
-        <v>45205.0</v>
+        <v>45205</v>
       </c>
       <c r="M3" s="5"/>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
+      <c r="N3" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
-        <v>9.64000000000002E14</v>
+        <v>964000000000002</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D4" s="7">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>14</v>
@@ -719,35 +757,38 @@
         <v>15</v>
       </c>
       <c r="G4" s="8">
-        <v>44958.0</v>
+        <v>44958</v>
       </c>
       <c r="H4" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="I4" s="9">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="J4" s="7"/>
       <c r="K4" s="5" t="s">
         <v>19</v>
       </c>
       <c r="L4" s="10">
-        <v>45239.0</v>
+        <v>45239</v>
       </c>
       <c r="M4" s="5"/>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
-        <v>9.64000000000003E14</v>
+        <v>964000000000003</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C5" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D5" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>14</v>
@@ -756,35 +797,38 @@
         <v>15</v>
       </c>
       <c r="G5" s="8">
-        <v>45113.0</v>
+        <v>45113</v>
       </c>
       <c r="H5" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I5" s="9">
-        <v>9.8</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="J5" s="7"/>
       <c r="K5" s="5" t="s">
         <v>16</v>
       </c>
       <c r="L5" s="10">
-        <v>45117.0</v>
+        <v>45117</v>
       </c>
       <c r="M5" s="5"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
-        <v>9.64000000000004E14</v>
+        <v>964000000000004</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C6" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D6" s="7">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>14</v>
@@ -793,10 +837,10 @@
         <v>15</v>
       </c>
       <c r="G6" s="8">
-        <v>45144.0</v>
+        <v>45144</v>
       </c>
       <c r="H6" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="9">
         <v>12.4</v>
@@ -806,22 +850,25 @@
         <v>16</v>
       </c>
       <c r="L6" s="10">
-        <v>44933.0</v>
+        <v>44933</v>
       </c>
       <c r="M6" s="5"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
-        <v>9.64000000000005E14</v>
+        <v>964000000000005</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D7" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>14</v>
@@ -830,10 +877,10 @@
         <v>23</v>
       </c>
       <c r="G7" s="8">
-        <v>45140.0</v>
+        <v>45140</v>
       </c>
       <c r="H7" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="7"/>
@@ -841,22 +888,25 @@
         <v>16</v>
       </c>
       <c r="L7" s="10">
-        <v>45021.0</v>
+        <v>45021</v>
       </c>
       <c r="M7" s="5"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
-        <v>9.64000000000006E14</v>
+        <v>964000000000006</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D8" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>14</v>
@@ -865,10 +915,10 @@
         <v>15</v>
       </c>
       <c r="G8" s="8">
-        <v>45145.0</v>
+        <v>45145</v>
       </c>
       <c r="H8" s="5">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="I8" s="9">
         <v>26.6</v>
@@ -878,23 +928,26 @@
         <v>16</v>
       </c>
       <c r="L8" s="10">
-        <v>45194.0</v>
+        <v>45194</v>
       </c>
       <c r="M8" s="5"/>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
       <c r="O8" s="12"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
-        <v>9.64000000000007E14</v>
+        <v>964000000000007</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D9" s="7">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>14</v>
@@ -903,10 +956,10 @@
         <v>15</v>
       </c>
       <c r="G9" s="8">
-        <v>45022.0</v>
+        <v>45022</v>
       </c>
       <c r="H9" s="5">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="I9" s="9">
         <v>16.8</v>
@@ -916,22 +969,25 @@
         <v>19</v>
       </c>
       <c r="L9" s="10">
-        <v>44967.0</v>
+        <v>44967</v>
       </c>
       <c r="M9" s="5"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
-        <v>9.64000000000008E14</v>
+        <v>964000000000008</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C10" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D10" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>14</v>
@@ -940,10 +996,10 @@
         <v>15</v>
       </c>
       <c r="G10" s="8">
-        <v>45262.0</v>
+        <v>45262</v>
       </c>
       <c r="H10" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="I10" s="9">
         <v>14.4</v>
@@ -953,22 +1009,25 @@
         <v>16</v>
       </c>
       <c r="L10" s="10">
-        <v>45269.0</v>
+        <v>45269</v>
       </c>
       <c r="M10" s="5"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
-        <v>9.64000000000009E14</v>
+        <v>964000000000009</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C11" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D11" s="7">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>14</v>
@@ -977,10 +1036,10 @@
         <v>23</v>
       </c>
       <c r="G11" s="8">
-        <v>44991.0</v>
+        <v>44991</v>
       </c>
       <c r="H11" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="7"/>
@@ -988,22 +1047,25 @@
         <v>16</v>
       </c>
       <c r="L11" s="10">
-        <v>45235.0</v>
+        <v>45235</v>
       </c>
       <c r="M11" s="5"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
-        <v>9.6400000000001E14</v>
+        <v>964000000000010</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C12" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D12" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>14</v>
@@ -1012,35 +1074,38 @@
         <v>15</v>
       </c>
       <c r="G12" s="8">
-        <v>44991.0</v>
+        <v>44991</v>
       </c>
       <c r="H12" s="5">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="I12" s="9">
-        <v>17.6</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="J12" s="7"/>
       <c r="K12" s="5" t="s">
         <v>16</v>
       </c>
       <c r="L12" s="10">
-        <v>44966.0</v>
+        <v>44966</v>
       </c>
       <c r="M12" s="5"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
-        <v>9.64000000000011E14</v>
+        <v>964000000000011</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C13" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D13" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>14</v>
@@ -1049,10 +1114,10 @@
         <v>15</v>
       </c>
       <c r="G13" s="8">
-        <v>45175.0</v>
+        <v>45175</v>
       </c>
       <c r="H13" s="5">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="I13" s="9">
         <v>20.5</v>
@@ -1062,22 +1127,25 @@
         <v>16</v>
       </c>
       <c r="L13" s="10">
-        <v>45088.0</v>
+        <v>45088</v>
       </c>
       <c r="M13" s="5"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
+      <c r="N13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
-        <v>9.64000000000012E14</v>
+        <v>964000000000012</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C14" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D14" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>14</v>
@@ -1086,35 +1154,38 @@
         <v>15</v>
       </c>
       <c r="G14" s="8">
-        <v>44933.0</v>
+        <v>44933</v>
       </c>
       <c r="H14" s="5">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="I14" s="9">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="5" t="s">
         <v>16</v>
       </c>
       <c r="L14" s="10">
-        <v>45223.0</v>
+        <v>45223</v>
       </c>
       <c r="M14" s="5"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
-        <v>9.64000000000013E14</v>
+        <v>964000000000013</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C15" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D15" s="7">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>14</v>
@@ -1123,10 +1194,10 @@
         <v>23</v>
       </c>
       <c r="G15" s="8">
-        <v>44811.0</v>
+        <v>44811</v>
       </c>
       <c r="H15" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="7"/>
@@ -1134,22 +1205,25 @@
         <v>16</v>
       </c>
       <c r="L15" s="10">
-        <v>45235.0</v>
+        <v>45235</v>
       </c>
       <c r="M15" s="5"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
+      <c r="N15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
-        <v>9.64000000000014E14</v>
+        <v>964000000000014</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C16" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D16" s="7">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>14</v>
@@ -1158,10 +1232,10 @@
         <v>15</v>
       </c>
       <c r="G16" s="8">
-        <v>45054.0</v>
+        <v>45054</v>
       </c>
       <c r="H16" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="I16" s="9">
         <v>15.8</v>
@@ -1171,22 +1245,25 @@
         <v>19</v>
       </c>
       <c r="L16" s="10">
-        <v>45208.0</v>
+        <v>45208</v>
       </c>
       <c r="M16" s="5"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
-        <v>9.64000000000015E14</v>
+        <v>964000000000015</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C17" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D17" s="7">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>14</v>
@@ -1195,35 +1272,38 @@
         <v>15</v>
       </c>
       <c r="G17" s="8">
-        <v>45052.0</v>
+        <v>45052</v>
       </c>
       <c r="H17" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="I17" s="9">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="J17" s="7"/>
       <c r="K17" s="5" t="s">
         <v>16</v>
       </c>
       <c r="L17" s="10">
-        <v>45025.0</v>
+        <v>45025</v>
       </c>
       <c r="M17" s="5"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
-        <v>9.64000000000016E14</v>
+        <v>964000000000016</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>34</v>
       </c>
       <c r="C18" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D18" s="7">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>14</v>
@@ -1232,10 +1312,10 @@
         <v>15</v>
       </c>
       <c r="G18" s="8">
-        <v>45083.0</v>
+        <v>45083</v>
       </c>
       <c r="H18" s="5">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="I18" s="9">
         <v>19.3</v>
@@ -1245,22 +1325,25 @@
         <v>19</v>
       </c>
       <c r="L18" s="10">
-        <v>45239.0</v>
+        <v>45239</v>
       </c>
       <c r="M18" s="5"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
+      <c r="N18" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
-        <v>9.64000000000017E14</v>
+        <v>964000000000017</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C19" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D19" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>14</v>
@@ -1269,10 +1352,10 @@
         <v>15</v>
       </c>
       <c r="G19" s="8">
-        <v>44811.0</v>
+        <v>44811</v>
       </c>
       <c r="H19" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I19" s="9">
         <v>11.8</v>
@@ -1282,22 +1365,25 @@
         <v>16</v>
       </c>
       <c r="L19" s="10">
-        <v>44967.0</v>
+        <v>44967</v>
       </c>
       <c r="M19" s="5"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
+      <c r="N19" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
-        <v>9.64000000000018E14</v>
+        <v>964000000000018</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C20" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D20" s="7">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>14</v>
@@ -1306,10 +1392,10 @@
         <v>23</v>
       </c>
       <c r="G20" s="8">
-        <v>44988.0</v>
+        <v>44988</v>
       </c>
       <c r="H20" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="7"/>
@@ -1317,22 +1403,25 @@
         <v>16</v>
       </c>
       <c r="L20" s="10">
-        <v>45051.0</v>
+        <v>45051</v>
       </c>
       <c r="M20" s="5"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
+      <c r="N20" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="5">
-        <v>9.64000000000019E14</v>
+        <v>964000000000019</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C21" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D21" s="7">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>14</v>
@@ -1341,10 +1430,10 @@
         <v>15</v>
       </c>
       <c r="G21" s="8">
-        <v>45206.0</v>
+        <v>45206</v>
       </c>
       <c r="H21" s="5">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="I21" s="9">
         <v>21.2</v>
@@ -1354,22 +1443,25 @@
         <v>16</v>
       </c>
       <c r="L21" s="10">
-        <v>44995.0</v>
+        <v>44995</v>
       </c>
       <c r="M21" s="5"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
+      <c r="N21" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
-        <v>9.6400000000002E14</v>
+        <v>964000000000020</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C22" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D22" s="7">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>14</v>
@@ -1381,32 +1473,35 @@
         <v>39</v>
       </c>
       <c r="H22" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="I22" s="9">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="5" t="s">
         <v>16</v>
       </c>
       <c r="L22" s="10">
-        <v>45269.0</v>
+        <v>45269</v>
       </c>
       <c r="M22" s="5"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
+      <c r="N22" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
-        <v>9.64000000000021E14</v>
+        <v>964000000000021</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C23" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D23" s="7">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>14</v>
@@ -1415,10 +1510,10 @@
         <v>15</v>
       </c>
       <c r="G23" s="8">
-        <v>45175.0</v>
+        <v>45175</v>
       </c>
       <c r="H23" s="5">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="I23" s="9">
         <v>15.2</v>
@@ -1428,22 +1523,25 @@
         <v>16</v>
       </c>
       <c r="L23" s="10">
-        <v>45025.0</v>
+        <v>45025</v>
       </c>
       <c r="M23" s="5"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
+      <c r="N23" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
-        <v>9.64000000000022E14</v>
+        <v>964000000000022</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C24" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D24" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>14</v>
@@ -1452,35 +1550,38 @@
         <v>15</v>
       </c>
       <c r="G24" s="8">
-        <v>44871.0</v>
+        <v>44871</v>
       </c>
       <c r="H24" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I24" s="9">
-        <v>9.2</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="J24" s="7"/>
       <c r="K24" s="5" t="s">
         <v>16</v>
       </c>
       <c r="L24" s="10">
-        <v>45175.0</v>
+        <v>45175</v>
       </c>
       <c r="M24" s="5"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
+      <c r="N24" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
-        <v>9.64000000000023E14</v>
+        <v>964000000000023</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>42</v>
       </c>
       <c r="C25" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D25" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>14</v>
@@ -1489,35 +1590,38 @@
         <v>15</v>
       </c>
       <c r="G25" s="8">
-        <v>45052.0</v>
+        <v>45052</v>
       </c>
       <c r="H25" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I25" s="9">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="J25" s="7"/>
       <c r="K25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="L25" s="10">
-        <v>45210.0</v>
+        <v>45210</v>
       </c>
       <c r="M25" s="5"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
+      <c r="N25" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
-        <v>9.64000000000024E14</v>
+        <v>964000000000024</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C26" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D26" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>14</v>
@@ -1526,10 +1630,10 @@
         <v>15</v>
       </c>
       <c r="G26" s="8">
-        <v>45113.0</v>
+        <v>45113</v>
       </c>
       <c r="H26" s="5">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="I26" s="9">
         <v>16.8</v>
@@ -1539,22 +1643,25 @@
         <v>16</v>
       </c>
       <c r="L26" s="10">
-        <v>45117.0</v>
+        <v>45117</v>
       </c>
       <c r="M26" s="5"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
+      <c r="N26" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
-        <v>9.64000000000025E14</v>
+        <v>964000000000025</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C27" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D27" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>14</v>
@@ -1563,35 +1670,38 @@
         <v>15</v>
       </c>
       <c r="G27" s="8">
-        <v>44933.0</v>
+        <v>44933</v>
       </c>
       <c r="H27" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="I27" s="9">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="J27" s="7"/>
       <c r="K27" s="5" t="s">
         <v>19</v>
       </c>
       <c r="L27" s="10">
-        <v>45147.0</v>
+        <v>45147</v>
       </c>
       <c r="M27" s="5"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
+      <c r="N27" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
-        <v>9.64000000000026E14</v>
+        <v>964000000000026</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C28" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D28" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>14</v>
@@ -1600,35 +1710,38 @@
         <v>15</v>
       </c>
       <c r="G28" s="8">
-        <v>44932.0</v>
+        <v>44932</v>
       </c>
       <c r="H28" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I28" s="9">
-        <v>10.2</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="J28" s="7"/>
       <c r="K28" s="5" t="s">
         <v>16</v>
       </c>
       <c r="L28" s="10">
-        <v>45082.0</v>
+        <v>45082</v>
       </c>
       <c r="M28" s="5"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
+      <c r="N28" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
-        <v>9.64000000000027E14</v>
+        <v>964000000000027</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C29" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D29" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>14</v>
@@ -1637,10 +1750,10 @@
         <v>23</v>
       </c>
       <c r="G29" s="8">
-        <v>44841.0</v>
+        <v>44841</v>
       </c>
       <c r="H29" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I29" s="9"/>
       <c r="J29" s="7"/>
@@ -1648,22 +1761,25 @@
         <v>16</v>
       </c>
       <c r="L29" s="10">
-        <v>45265.0</v>
+        <v>45265</v>
       </c>
       <c r="M29" s="5"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
+      <c r="N29" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
-        <v>9.64000000000028E14</v>
+        <v>964000000000028</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>47</v>
       </c>
       <c r="C30" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D30" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>14</v>
@@ -1672,35 +1788,38 @@
         <v>15</v>
       </c>
       <c r="G30" s="8">
-        <v>45267.0</v>
+        <v>45267</v>
       </c>
       <c r="H30" s="5">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="I30" s="9">
-        <v>18.6</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="J30" s="7"/>
       <c r="K30" s="5" t="s">
         <v>19</v>
       </c>
       <c r="L30" s="10">
-        <v>44936.0</v>
+        <v>44936</v>
       </c>
       <c r="M30" s="5"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
+      <c r="N30" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
-        <v>9.64000000000029E14</v>
+        <v>964000000000029</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>48</v>
       </c>
       <c r="C31" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D31" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>14</v>
@@ -1709,10 +1828,10 @@
         <v>23</v>
       </c>
       <c r="G31" s="8">
-        <v>45232.0</v>
+        <v>45232</v>
       </c>
       <c r="H31" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I31" s="9"/>
       <c r="J31" s="7"/>
@@ -1720,22 +1839,25 @@
         <v>16</v>
       </c>
       <c r="L31" s="10">
-        <v>45082.0</v>
+        <v>45082</v>
       </c>
       <c r="M31" s="5"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
+      <c r="N31" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="5">
-        <v>9.6400000000003E14</v>
+        <v>964000000000030</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C32" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D32" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>14</v>
@@ -1744,10 +1866,10 @@
         <v>15</v>
       </c>
       <c r="G32" s="8">
-        <v>45178.0</v>
+        <v>45178</v>
       </c>
       <c r="H32" s="5">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="I32" s="9">
         <v>20.3</v>
@@ -1757,22 +1879,25 @@
         <v>19</v>
       </c>
       <c r="L32" s="10">
-        <v>44967.0</v>
+        <v>44967</v>
       </c>
       <c r="M32" s="5"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
+      <c r="N32" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5">
-        <v>9.64000000000031E14</v>
+        <v>964000000000031</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C33" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D33" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>14</v>
@@ -1781,10 +1906,10 @@
         <v>23</v>
       </c>
       <c r="G33" s="8">
-        <v>45019.0</v>
+        <v>45019</v>
       </c>
       <c r="H33" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I33" s="9">
         <v>12.2</v>
@@ -1794,22 +1919,25 @@
         <v>16</v>
       </c>
       <c r="L33" s="10">
-        <v>45143.0</v>
+        <v>45143</v>
       </c>
       <c r="M33" s="5"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
+      <c r="N33" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="5">
-        <v>9.64000000000032E14</v>
+        <v>964000000000032</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>51</v>
       </c>
       <c r="C34" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D34" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>14</v>
@@ -1818,10 +1946,10 @@
         <v>15</v>
       </c>
       <c r="G34" s="8">
-        <v>45055.0</v>
+        <v>45055</v>
       </c>
       <c r="H34" s="5">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="I34" s="9">
         <v>17.8</v>
@@ -1831,22 +1959,25 @@
         <v>19</v>
       </c>
       <c r="L34" s="10">
-        <v>45209.0</v>
+        <v>45209</v>
       </c>
       <c r="M34" s="5"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
+      <c r="N34" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="5">
-        <v>9.64000000000033E14</v>
+        <v>964000000000033</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>52</v>
       </c>
       <c r="C35" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D35" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>14</v>
@@ -1855,35 +1986,38 @@
         <v>15</v>
       </c>
       <c r="G35" s="8">
-        <v>45115.0</v>
+        <v>45115</v>
       </c>
       <c r="H35" s="5">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="I35" s="9">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="J35" s="7"/>
       <c r="K35" s="5" t="s">
         <v>16</v>
       </c>
       <c r="L35" s="10">
-        <v>44995.0</v>
+        <v>44995</v>
       </c>
       <c r="M35" s="5"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
+      <c r="N35" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="5">
-        <v>9.64000000000034E14</v>
+        <v>964000000000034</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C36" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D36" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>14</v>
@@ -1892,10 +2026,10 @@
         <v>15</v>
       </c>
       <c r="G36" s="8">
-        <v>45177.0</v>
+        <v>45177</v>
       </c>
       <c r="H36" s="5">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="I36" s="9">
         <v>21.6</v>
@@ -1905,22 +2039,25 @@
         <v>19</v>
       </c>
       <c r="L36" s="10">
-        <v>45143.0</v>
+        <v>45143</v>
       </c>
       <c r="M36" s="5"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
+      <c r="N36" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="5">
-        <v>9.64000000000035E14</v>
+        <v>964000000000035</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>54</v>
       </c>
       <c r="C37" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D37" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>14</v>
@@ -1929,35 +2066,38 @@
         <v>15</v>
       </c>
       <c r="G37" s="8">
-        <v>44993.0</v>
+        <v>44993</v>
       </c>
       <c r="H37" s="5">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="I37" s="9">
-        <v>19.6</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="J37" s="7"/>
       <c r="K37" s="5" t="s">
         <v>19</v>
       </c>
       <c r="L37" s="10">
-        <v>45055.0</v>
+        <v>45055</v>
       </c>
       <c r="M37" s="5"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
+      <c r="N37" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="5">
-        <v>9.64000000000036E14</v>
+        <v>964000000000036</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>55</v>
       </c>
       <c r="C38" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D38" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>56</v>
@@ -1966,10 +2106,10 @@
         <v>23</v>
       </c>
       <c r="G38" s="8">
-        <v>45109.0</v>
+        <v>45109</v>
       </c>
       <c r="H38" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I38" s="9"/>
       <c r="J38" s="7"/>
@@ -1977,22 +2117,25 @@
         <v>16</v>
       </c>
       <c r="L38" s="10">
-        <v>45235.0</v>
+        <v>45235</v>
       </c>
       <c r="M38" s="5"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
+      <c r="N38" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="5">
-        <v>9.64000000000037E14</v>
+        <v>964000000000037</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>57</v>
       </c>
       <c r="C39" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D39" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>56</v>
@@ -2001,35 +2144,38 @@
         <v>15</v>
       </c>
       <c r="G39" s="8">
-        <v>45175.0</v>
+        <v>45175</v>
       </c>
       <c r="H39" s="5">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="I39" s="9">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="J39" s="7"/>
       <c r="K39" s="5" t="s">
         <v>19</v>
       </c>
       <c r="L39" s="10">
-        <v>45235.0</v>
+        <v>45235</v>
       </c>
       <c r="M39" s="5"/>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
+      <c r="N39" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="5">
-        <v>9.64000000000038E14</v>
+        <v>964000000000038</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>58</v>
       </c>
       <c r="C40" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D40" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>56</v>
@@ -2038,10 +2184,10 @@
         <v>23</v>
       </c>
       <c r="G40" s="8">
-        <v>45109.0</v>
+        <v>45109</v>
       </c>
       <c r="H40" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I40" s="9"/>
       <c r="J40" s="7"/>
@@ -2049,22 +2195,25 @@
         <v>16</v>
       </c>
       <c r="L40" s="10">
-        <v>45208.0</v>
+        <v>45208</v>
       </c>
       <c r="M40" s="5"/>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
+      <c r="N40" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5">
-        <v>9.64000000000039E14</v>
+        <v>964000000000039</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>59</v>
       </c>
       <c r="C41" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D41" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>56</v>
@@ -2073,10 +2222,10 @@
         <v>15</v>
       </c>
       <c r="G41" s="8">
-        <v>45140.0</v>
+        <v>45140</v>
       </c>
       <c r="H41" s="5">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="I41" s="9">
         <v>17.5</v>
@@ -2086,22 +2235,25 @@
         <v>16</v>
       </c>
       <c r="L41" s="10">
-        <v>45208.0</v>
+        <v>45208</v>
       </c>
       <c r="M41" s="5"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
+      <c r="N41" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="5">
-        <v>9.6400000000004E14</v>
+        <v>964000000000040</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>60</v>
       </c>
       <c r="C42" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D42" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>56</v>
@@ -2110,35 +2262,38 @@
         <v>15</v>
       </c>
       <c r="G42" s="8">
-        <v>44993.0</v>
+        <v>44993</v>
       </c>
       <c r="H42" s="5">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="I42" s="9">
-        <v>16.6</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="J42" s="7"/>
       <c r="K42" s="5" t="s">
         <v>16</v>
       </c>
       <c r="L42" s="10">
-        <v>45088.0</v>
+        <v>45088</v>
       </c>
       <c r="M42" s="5"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
+      <c r="N42" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="5">
-        <v>9.64000000000041E14</v>
+        <v>964000000000041</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>61</v>
       </c>
       <c r="C43" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D43" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>56</v>
@@ -2147,35 +2302,38 @@
         <v>15</v>
       </c>
       <c r="G43" s="8">
-        <v>45266.0</v>
+        <v>45266</v>
       </c>
       <c r="H43" s="5">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="I43" s="9">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="J43" s="7"/>
       <c r="K43" s="5" t="s">
         <v>16</v>
       </c>
       <c r="L43" s="10">
-        <v>45088.0</v>
+        <v>45088</v>
       </c>
       <c r="M43" s="5"/>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
+      <c r="N43" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="5">
-        <v>9.64000000000042E14</v>
+        <v>964000000000042</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>62</v>
       </c>
       <c r="C44" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D44" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>14</v>
@@ -2184,10 +2342,10 @@
         <v>15</v>
       </c>
       <c r="G44" s="8">
-        <v>45175.0</v>
+        <v>45175</v>
       </c>
       <c r="H44" s="5">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="I44" s="9">
         <v>20.6</v>
@@ -2197,22 +2355,25 @@
         <v>16</v>
       </c>
       <c r="L44" s="10">
-        <v>45175.0</v>
+        <v>45175</v>
       </c>
       <c r="M44" s="5"/>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
+      <c r="N44" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="5">
-        <v>9.64000000000043E14</v>
+        <v>964000000000043</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>63</v>
       </c>
       <c r="C45" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D45" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>14</v>
@@ -2221,10 +2382,10 @@
         <v>23</v>
       </c>
       <c r="G45" s="8">
-        <v>45177.0</v>
+        <v>45177</v>
       </c>
       <c r="H45" s="11">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="7"/>
@@ -2232,22 +2393,25 @@
         <v>16</v>
       </c>
       <c r="L45" s="10">
-        <v>45175.0</v>
+        <v>45175</v>
       </c>
       <c r="M45" s="5"/>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
+      <c r="N45" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="5">
-        <v>9.64000000000044E14</v>
+        <v>964000000000044</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>64</v>
       </c>
       <c r="C46" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D46" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E46" s="5" t="s">
         <v>14</v>
@@ -2256,35 +2420,38 @@
         <v>15</v>
       </c>
       <c r="G46" s="8">
-        <v>45086.0</v>
+        <v>45086</v>
       </c>
       <c r="H46" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="I46" s="9">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="J46" s="7"/>
       <c r="K46" s="5" t="s">
         <v>16</v>
       </c>
       <c r="L46" s="10">
-        <v>45239.0</v>
+        <v>45239</v>
       </c>
       <c r="M46" s="5"/>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
+      <c r="N46" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="5">
-        <v>9.64000000000045E14</v>
+        <v>964000000000045</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>65</v>
       </c>
       <c r="C47" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D47" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>56</v>
@@ -2293,10 +2460,10 @@
         <v>15</v>
       </c>
       <c r="G47" s="8">
-        <v>45201.0</v>
+        <v>45201</v>
       </c>
       <c r="H47" s="5">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="I47" s="9">
         <v>13.2</v>
@@ -2306,22 +2473,25 @@
         <v>16</v>
       </c>
       <c r="L47" s="10">
-        <v>45210.0</v>
+        <v>45210</v>
       </c>
       <c r="M47" s="5"/>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
+      <c r="N47" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="5">
-        <v>9.64000000000046E14</v>
+        <v>964000000000046</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>66</v>
       </c>
       <c r="C48" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D48" s="7">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>56</v>
@@ -2330,10 +2500,10 @@
         <v>15</v>
       </c>
       <c r="G48" s="8">
-        <v>45113.0</v>
+        <v>45113</v>
       </c>
       <c r="H48" s="5">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="I48" s="9">
         <v>17.8</v>
@@ -2343,22 +2513,25 @@
         <v>19</v>
       </c>
       <c r="L48" s="10">
-        <v>45210.0</v>
+        <v>45210</v>
       </c>
       <c r="M48" s="5"/>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
+      <c r="N48" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="5">
-        <v>9.64000000000047E14</v>
+        <v>964000000000047</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>67</v>
       </c>
       <c r="C49" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D49" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>56</v>
@@ -2367,13 +2540,13 @@
         <v>15</v>
       </c>
       <c r="G49" s="8">
-        <v>45263.0</v>
+        <v>45263</v>
       </c>
       <c r="H49" s="5">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="I49" s="9">
-        <v>16.4</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="J49" s="7"/>
       <c r="K49" s="5" t="s">
@@ -2383,19 +2556,22 @@
         <v>68</v>
       </c>
       <c r="M49" s="5"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
+      <c r="N49" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="5">
-        <v>9.64000000000048E14</v>
+        <v>964000000000048</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>69</v>
       </c>
       <c r="C50" s="6">
-        <v>45321.0</v>
+        <v>45321</v>
       </c>
       <c r="D50" s="7">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>14</v>
@@ -2404,10 +2580,10 @@
         <v>15</v>
       </c>
       <c r="G50" s="8">
-        <v>45144.0</v>
+        <v>45144</v>
       </c>
       <c r="H50" s="5">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I50" s="9">
         <v>6.2</v>
@@ -2420,1956 +2596,1959 @@
         <v>68</v>
       </c>
       <c r="M50" s="5"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
+      <c r="N50" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C51" s="12"/>
       <c r="G51" s="13"/>
       <c r="I51" s="14"/>
       <c r="L51" s="13"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C52" s="12"/>
       <c r="G52" s="13"/>
       <c r="L52" s="13"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C53" s="12"/>
       <c r="G53" s="13"/>
       <c r="L53" s="13"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C54" s="12"/>
       <c r="G54" s="13"/>
       <c r="I54" s="14"/>
       <c r="L54" s="13"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C55" s="12"/>
       <c r="G55" s="13"/>
       <c r="I55" s="14"/>
       <c r="L55" s="13"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C56" s="12"/>
       <c r="G56" s="13"/>
       <c r="I56" s="14"/>
       <c r="L56" s="13"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C57" s="12"/>
       <c r="G57" s="13"/>
       <c r="I57" s="14"/>
       <c r="L57" s="13"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C58" s="12"/>
       <c r="G58" s="13"/>
       <c r="I58" s="14"/>
       <c r="L58" s="13"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C59" s="12"/>
       <c r="G59" s="13"/>
       <c r="I59" s="14"/>
       <c r="L59" s="13"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C60" s="12"/>
       <c r="G60" s="13"/>
       <c r="I60" s="14"/>
       <c r="L60" s="13"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C61" s="12"/>
       <c r="G61" s="13"/>
       <c r="I61" s="14"/>
       <c r="L61" s="13"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C62" s="12"/>
       <c r="G62" s="13"/>
       <c r="I62" s="14"/>
       <c r="L62" s="13"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C63" s="12"/>
       <c r="G63" s="13"/>
       <c r="I63" s="14"/>
       <c r="L63" s="13"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C64" s="12"/>
       <c r="G64" s="13"/>
       <c r="I64" s="14"/>
       <c r="L64" s="13"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C65" s="12"/>
       <c r="G65" s="13"/>
       <c r="I65" s="14"/>
       <c r="L65" s="13"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C66" s="12"/>
       <c r="G66" s="13"/>
       <c r="I66" s="14"/>
       <c r="L66" s="13"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C67" s="12"/>
       <c r="G67" s="13"/>
       <c r="I67" s="14"/>
       <c r="L67" s="13"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C68" s="12"/>
       <c r="G68" s="13"/>
       <c r="I68" s="14"/>
       <c r="L68" s="13"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C69" s="12"/>
       <c r="G69" s="13"/>
       <c r="I69" s="14"/>
       <c r="L69" s="13"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C70" s="12"/>
       <c r="G70" s="13"/>
       <c r="I70" s="14"/>
       <c r="L70" s="13"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C71" s="12"/>
       <c r="G71" s="13"/>
       <c r="I71" s="14"/>
       <c r="L71" s="13"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C72" s="12"/>
       <c r="G72" s="13"/>
       <c r="I72" s="14"/>
       <c r="L72" s="13"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C73" s="12"/>
       <c r="G73" s="13"/>
       <c r="I73" s="14"/>
       <c r="L73" s="13"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C74" s="12"/>
       <c r="G74" s="13"/>
       <c r="I74" s="14"/>
       <c r="L74" s="13"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C75" s="12"/>
       <c r="G75" s="13"/>
       <c r="I75" s="14"/>
       <c r="L75" s="13"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C76" s="12"/>
       <c r="G76" s="13"/>
       <c r="I76" s="14"/>
       <c r="L76" s="13"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C77" s="12"/>
       <c r="G77" s="13"/>
       <c r="I77" s="14"/>
       <c r="L77" s="13"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C78" s="12"/>
       <c r="G78" s="13"/>
       <c r="I78" s="14"/>
       <c r="L78" s="13"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C79" s="12"/>
       <c r="G79" s="13"/>
       <c r="I79" s="14"/>
       <c r="L79" s="13"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C80" s="12"/>
       <c r="G80" s="13"/>
       <c r="I80" s="14"/>
       <c r="L80" s="13"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C81" s="12"/>
       <c r="G81" s="13"/>
       <c r="I81" s="14"/>
       <c r="L81" s="13"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C82" s="12"/>
       <c r="G82" s="13"/>
       <c r="I82" s="14"/>
       <c r="L82" s="13"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C83" s="12"/>
       <c r="G83" s="13"/>
       <c r="I83" s="14"/>
       <c r="L83" s="13"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C84" s="12"/>
       <c r="G84" s="13"/>
       <c r="I84" s="14"/>
       <c r="L84" s="13"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C85" s="12"/>
       <c r="G85" s="13"/>
       <c r="I85" s="14"/>
       <c r="L85" s="13"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C86" s="12"/>
       <c r="G86" s="13"/>
       <c r="I86" s="14"/>
       <c r="L86" s="13"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C87" s="12"/>
       <c r="G87" s="13"/>
       <c r="I87" s="14"/>
       <c r="L87" s="13"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C88" s="12"/>
       <c r="G88" s="13"/>
       <c r="I88" s="14"/>
       <c r="L88" s="13"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C89" s="12"/>
       <c r="G89" s="13"/>
       <c r="I89" s="14"/>
       <c r="L89" s="13"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C90" s="12"/>
       <c r="G90" s="13"/>
       <c r="I90" s="14"/>
       <c r="L90" s="13"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C91" s="12"/>
       <c r="G91" s="13"/>
       <c r="I91" s="14"/>
       <c r="L91" s="13"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C92" s="12"/>
       <c r="G92" s="13"/>
       <c r="I92" s="14"/>
       <c r="L92" s="13"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C93" s="12"/>
       <c r="G93" s="13"/>
       <c r="I93" s="14"/>
       <c r="L93" s="13"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C94" s="12"/>
       <c r="G94" s="13"/>
       <c r="I94" s="14"/>
       <c r="L94" s="13"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C95" s="12"/>
       <c r="G95" s="13"/>
       <c r="I95" s="14"/>
       <c r="L95" s="13"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C96" s="12"/>
       <c r="G96" s="13"/>
       <c r="I96" s="14"/>
       <c r="L96" s="13"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C97" s="12"/>
       <c r="G97" s="13"/>
       <c r="I97" s="14"/>
       <c r="L97" s="13"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C98" s="12"/>
       <c r="G98" s="13"/>
       <c r="I98" s="14"/>
       <c r="L98" s="13"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C99" s="12"/>
       <c r="G99" s="13"/>
       <c r="I99" s="14"/>
       <c r="L99" s="13"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C100" s="12"/>
       <c r="G100" s="13"/>
       <c r="I100" s="14"/>
       <c r="L100" s="13"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C101" s="12"/>
       <c r="G101" s="13"/>
       <c r="I101" s="14"/>
       <c r="L101" s="13"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C102" s="12"/>
       <c r="G102" s="13"/>
       <c r="I102" s="14"/>
       <c r="L102" s="13"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C103" s="12"/>
       <c r="G103" s="13"/>
       <c r="I103" s="14"/>
       <c r="L103" s="13"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C104" s="12"/>
       <c r="G104" s="13"/>
       <c r="I104" s="14"/>
       <c r="L104" s="13"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C105" s="12"/>
       <c r="G105" s="13"/>
       <c r="I105" s="14"/>
       <c r="L105" s="13"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C106" s="12"/>
       <c r="G106" s="13"/>
       <c r="I106" s="14"/>
       <c r="L106" s="13"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C107" s="12"/>
       <c r="G107" s="13"/>
       <c r="I107" s="14"/>
       <c r="L107" s="13"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C108" s="12"/>
       <c r="G108" s="13"/>
       <c r="I108" s="14"/>
       <c r="L108" s="13"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C109" s="12"/>
       <c r="G109" s="13"/>
       <c r="I109" s="14"/>
       <c r="L109" s="13"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C110" s="12"/>
       <c r="G110" s="13"/>
       <c r="I110" s="14"/>
       <c r="L110" s="13"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C111" s="12"/>
       <c r="G111" s="13"/>
       <c r="I111" s="14"/>
       <c r="L111" s="13"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C112" s="12"/>
       <c r="G112" s="13"/>
       <c r="I112" s="14"/>
       <c r="L112" s="13"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C113" s="12"/>
       <c r="G113" s="13"/>
       <c r="I113" s="14"/>
       <c r="L113" s="13"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C114" s="12"/>
       <c r="G114" s="13"/>
       <c r="I114" s="14"/>
       <c r="L114" s="13"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C115" s="12"/>
       <c r="G115" s="13"/>
       <c r="I115" s="14"/>
       <c r="L115" s="13"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C116" s="12"/>
       <c r="G116" s="13"/>
       <c r="I116" s="14"/>
       <c r="L116" s="13"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C117" s="12"/>
       <c r="G117" s="13"/>
       <c r="I117" s="14"/>
       <c r="L117" s="13"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C118" s="12"/>
       <c r="G118" s="13"/>
       <c r="I118" s="14"/>
       <c r="L118" s="13"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C119" s="12"/>
       <c r="G119" s="13"/>
       <c r="I119" s="14"/>
       <c r="L119" s="13"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C120" s="12"/>
       <c r="G120" s="13"/>
       <c r="I120" s="14"/>
       <c r="L120" s="13"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C121" s="12"/>
       <c r="G121" s="13"/>
       <c r="I121" s="14"/>
       <c r="L121" s="13"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C122" s="12"/>
       <c r="G122" s="13"/>
       <c r="I122" s="14"/>
       <c r="L122" s="13"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row r="123" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C123" s="12"/>
       <c r="G123" s="13"/>
       <c r="I123" s="14"/>
       <c r="L123" s="13"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row r="124" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C124" s="12"/>
       <c r="G124" s="13"/>
       <c r="I124" s="14"/>
       <c r="L124" s="13"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row r="125" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C125" s="12"/>
       <c r="G125" s="13"/>
       <c r="I125" s="14"/>
       <c r="L125" s="13"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row r="126" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C126" s="12"/>
       <c r="G126" s="13"/>
       <c r="I126" s="14"/>
       <c r="L126" s="13"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
+    <row r="127" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C127" s="12"/>
       <c r="G127" s="13"/>
       <c r="I127" s="14"/>
       <c r="L127" s="13"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1">
+    <row r="128" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C128" s="12"/>
       <c r="G128" s="13"/>
       <c r="I128" s="14"/>
       <c r="L128" s="13"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1">
+    <row r="129" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C129" s="12"/>
       <c r="G129" s="13"/>
       <c r="I129" s="14"/>
       <c r="L129" s="13"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1">
+    <row r="130" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C130" s="12"/>
       <c r="G130" s="13"/>
       <c r="I130" s="14"/>
       <c r="L130" s="13"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1">
+    <row r="131" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C131" s="12"/>
       <c r="G131" s="13"/>
       <c r="I131" s="14"/>
       <c r="L131" s="13"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1">
+    <row r="132" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C132" s="12"/>
       <c r="G132" s="13"/>
       <c r="I132" s="14"/>
       <c r="L132" s="13"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1">
+    <row r="133" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C133" s="12"/>
       <c r="G133" s="13"/>
       <c r="I133" s="14"/>
       <c r="L133" s="13"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1">
+    <row r="134" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C134" s="12"/>
       <c r="G134" s="13"/>
       <c r="I134" s="14"/>
       <c r="L134" s="13"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1">
+    <row r="135" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C135" s="12"/>
       <c r="G135" s="13"/>
       <c r="I135" s="14"/>
       <c r="L135" s="13"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1">
+    <row r="136" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C136" s="12"/>
       <c r="G136" s="13"/>
       <c r="I136" s="14"/>
       <c r="L136" s="13"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
+    <row r="137" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C137" s="12"/>
       <c r="G137" s="13"/>
       <c r="I137" s="14"/>
       <c r="L137" s="13"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1">
+    <row r="138" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C138" s="12"/>
       <c r="G138" s="13"/>
       <c r="I138" s="14"/>
       <c r="L138" s="13"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1">
+    <row r="139" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C139" s="12"/>
       <c r="G139" s="13"/>
       <c r="I139" s="14"/>
       <c r="L139" s="13"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
+    <row r="140" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C140" s="12"/>
       <c r="G140" s="13"/>
       <c r="I140" s="14"/>
       <c r="L140" s="13"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1">
+    <row r="141" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C141" s="12"/>
       <c r="G141" s="13"/>
       <c r="I141" s="14"/>
       <c r="L141" s="13"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
+    <row r="142" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C142" s="12"/>
       <c r="G142" s="13"/>
       <c r="I142" s="14"/>
       <c r="L142" s="13"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1">
+    <row r="143" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C143" s="12"/>
       <c r="G143" s="13"/>
       <c r="I143" s="14"/>
       <c r="L143" s="13"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1">
+    <row r="144" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C144" s="12"/>
       <c r="G144" s="13"/>
       <c r="I144" s="14"/>
       <c r="L144" s="13"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1">
+    <row r="145" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C145" s="12"/>
       <c r="G145" s="13"/>
       <c r="I145" s="14"/>
       <c r="L145" s="13"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1">
+    <row r="146" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C146" s="12"/>
       <c r="G146" s="13"/>
       <c r="I146" s="14"/>
       <c r="L146" s="13"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1">
+    <row r="147" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C147" s="12"/>
       <c r="G147" s="13"/>
       <c r="I147" s="14"/>
       <c r="L147" s="13"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1">
+    <row r="148" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C148" s="12"/>
       <c r="G148" s="13"/>
       <c r="I148" s="14"/>
       <c r="L148" s="13"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1">
+    <row r="149" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C149" s="12"/>
       <c r="G149" s="13"/>
       <c r="I149" s="14"/>
       <c r="L149" s="13"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
+    <row r="150" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C150" s="12"/>
       <c r="G150" s="13"/>
       <c r="I150" s="14"/>
       <c r="L150" s="13"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1">
+    <row r="151" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C151" s="12"/>
       <c r="G151" s="13"/>
       <c r="I151" s="14"/>
       <c r="L151" s="13"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1">
+    <row r="152" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C152" s="12"/>
       <c r="G152" s="13"/>
       <c r="I152" s="14"/>
       <c r="L152" s="13"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
+    <row r="153" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C153" s="12"/>
       <c r="G153" s="13"/>
       <c r="I153" s="14"/>
       <c r="L153" s="13"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1">
+    <row r="154" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C154" s="12"/>
       <c r="G154" s="13"/>
       <c r="I154" s="14"/>
       <c r="L154" s="13"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1">
+    <row r="155" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C155" s="12"/>
       <c r="G155" s="13"/>
       <c r="I155" s="14"/>
       <c r="L155" s="13"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1">
+    <row r="156" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C156" s="12"/>
       <c r="G156" s="13"/>
       <c r="I156" s="14"/>
       <c r="L156" s="13"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1">
+    <row r="157" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C157" s="12"/>
       <c r="G157" s="13"/>
       <c r="I157" s="14"/>
       <c r="L157" s="13"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1">
+    <row r="158" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C158" s="12"/>
       <c r="G158" s="13"/>
       <c r="I158" s="14"/>
       <c r="L158" s="13"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1">
+    <row r="159" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C159" s="12"/>
       <c r="G159" s="13"/>
       <c r="I159" s="14"/>
       <c r="L159" s="13"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1">
+    <row r="160" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C160" s="12"/>
       <c r="G160" s="13"/>
       <c r="I160" s="14"/>
       <c r="L160" s="13"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1">
+    <row r="161" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C161" s="12"/>
       <c r="G161" s="13"/>
       <c r="I161" s="14"/>
       <c r="L161" s="13"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1">
+    <row r="162" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C162" s="12"/>
       <c r="G162" s="13"/>
       <c r="I162" s="14"/>
       <c r="L162" s="13"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1">
+    <row r="163" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C163" s="12"/>
       <c r="G163" s="13"/>
       <c r="I163" s="14"/>
       <c r="L163" s="13"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1">
+    <row r="164" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C164" s="12"/>
       <c r="G164" s="13"/>
       <c r="I164" s="14"/>
       <c r="L164" s="13"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1">
+    <row r="165" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C165" s="12"/>
       <c r="G165" s="13"/>
       <c r="I165" s="14"/>
       <c r="L165" s="13"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1">
+    <row r="166" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C166" s="12"/>
       <c r="G166" s="13"/>
       <c r="I166" s="14"/>
       <c r="L166" s="13"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
+    <row r="167" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C167" s="12"/>
       <c r="G167" s="13"/>
       <c r="I167" s="14"/>
       <c r="L167" s="13"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
+    <row r="168" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C168" s="12"/>
       <c r="G168" s="13"/>
       <c r="I168" s="14"/>
       <c r="L168" s="13"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
+    <row r="169" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C169" s="12"/>
       <c r="G169" s="13"/>
       <c r="I169" s="14"/>
       <c r="L169" s="13"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
+    <row r="170" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C170" s="12"/>
       <c r="G170" s="13"/>
       <c r="I170" s="14"/>
       <c r="L170" s="13"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
+    <row r="171" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C171" s="12"/>
       <c r="G171" s="13"/>
       <c r="I171" s="14"/>
       <c r="L171" s="13"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
+    <row r="172" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C172" s="12"/>
       <c r="G172" s="13"/>
       <c r="I172" s="14"/>
       <c r="L172" s="13"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
+    <row r="173" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C173" s="12"/>
       <c r="G173" s="13"/>
       <c r="I173" s="14"/>
       <c r="L173" s="13"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
+    <row r="174" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C174" s="12"/>
       <c r="G174" s="13"/>
       <c r="I174" s="14"/>
       <c r="L174" s="13"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
+    <row r="175" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C175" s="12"/>
       <c r="G175" s="13"/>
       <c r="I175" s="14"/>
       <c r="L175" s="13"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
+    <row r="176" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C176" s="12"/>
       <c r="G176" s="13"/>
       <c r="I176" s="14"/>
       <c r="L176" s="13"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
+    <row r="177" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C177" s="12"/>
       <c r="G177" s="13"/>
       <c r="I177" s="14"/>
       <c r="L177" s="13"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
+    <row r="178" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C178" s="12"/>
       <c r="G178" s="13"/>
       <c r="I178" s="14"/>
       <c r="L178" s="13"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1">
+    <row r="179" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C179" s="12"/>
       <c r="G179" s="13"/>
       <c r="I179" s="14"/>
       <c r="L179" s="13"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1">
+    <row r="180" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C180" s="12"/>
       <c r="G180" s="13"/>
       <c r="I180" s="14"/>
       <c r="L180" s="13"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1">
+    <row r="181" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C181" s="12"/>
       <c r="G181" s="13"/>
       <c r="I181" s="14"/>
       <c r="L181" s="13"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
+    <row r="182" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C182" s="12"/>
       <c r="G182" s="13"/>
       <c r="I182" s="14"/>
       <c r="L182" s="13"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1">
+    <row r="183" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C183" s="12"/>
       <c r="G183" s="13"/>
       <c r="I183" s="14"/>
       <c r="L183" s="13"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1">
+    <row r="184" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C184" s="12"/>
       <c r="G184" s="13"/>
       <c r="I184" s="14"/>
       <c r="L184" s="13"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1">
+    <row r="185" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C185" s="12"/>
       <c r="G185" s="13"/>
       <c r="I185" s="14"/>
       <c r="L185" s="13"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1">
+    <row r="186" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C186" s="12"/>
       <c r="G186" s="13"/>
       <c r="I186" s="14"/>
       <c r="L186" s="13"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1">
+    <row r="187" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C187" s="12"/>
       <c r="G187" s="13"/>
       <c r="I187" s="14"/>
       <c r="L187" s="13"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1">
+    <row r="188" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C188" s="12"/>
       <c r="G188" s="13"/>
       <c r="I188" s="14"/>
       <c r="L188" s="13"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1">
+    <row r="189" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C189" s="12"/>
       <c r="G189" s="13"/>
       <c r="I189" s="14"/>
       <c r="L189" s="13"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1">
+    <row r="190" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C190" s="12"/>
       <c r="G190" s="13"/>
       <c r="I190" s="14"/>
       <c r="L190" s="13"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1">
+    <row r="191" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C191" s="12"/>
       <c r="G191" s="13"/>
       <c r="I191" s="14"/>
       <c r="L191" s="13"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1">
+    <row r="192" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C192" s="12"/>
       <c r="G192" s="13"/>
       <c r="I192" s="14"/>
       <c r="L192" s="13"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1">
+    <row r="193" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C193" s="12"/>
       <c r="G193" s="13"/>
       <c r="I193" s="14"/>
       <c r="L193" s="13"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1">
+    <row r="194" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C194" s="12"/>
       <c r="G194" s="13"/>
       <c r="I194" s="14"/>
       <c r="L194" s="13"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1">
+    <row r="195" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C195" s="12"/>
       <c r="G195" s="13"/>
       <c r="I195" s="14"/>
       <c r="L195" s="13"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1">
+    <row r="196" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C196" s="12"/>
       <c r="G196" s="13"/>
       <c r="I196" s="14"/>
       <c r="L196" s="13"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1">
+    <row r="197" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C197" s="12"/>
       <c r="G197" s="13"/>
       <c r="I197" s="14"/>
       <c r="L197" s="13"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1">
+    <row r="198" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C198" s="12"/>
       <c r="G198" s="13"/>
       <c r="I198" s="14"/>
       <c r="L198" s="13"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1">
+    <row r="199" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C199" s="12"/>
       <c r="G199" s="13"/>
       <c r="I199" s="14"/>
       <c r="L199" s="13"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1">
+    <row r="200" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C200" s="12"/>
       <c r="G200" s="13"/>
       <c r="I200" s="14"/>
       <c r="L200" s="13"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1">
+    <row r="201" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C201" s="12"/>
       <c r="G201" s="13"/>
       <c r="I201" s="14"/>
       <c r="L201" s="13"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1">
+    <row r="202" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C202" s="12"/>
       <c r="G202" s="13"/>
       <c r="I202" s="14"/>
       <c r="L202" s="13"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1">
+    <row r="203" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C203" s="12"/>
       <c r="G203" s="13"/>
       <c r="I203" s="14"/>
       <c r="L203" s="13"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1">
+    <row r="204" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C204" s="12"/>
       <c r="G204" s="13"/>
       <c r="I204" s="14"/>
       <c r="L204" s="13"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1">
+    <row r="205" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C205" s="12"/>
       <c r="G205" s="13"/>
       <c r="I205" s="14"/>
       <c r="L205" s="13"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1">
+    <row r="206" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C206" s="12"/>
       <c r="G206" s="13"/>
       <c r="I206" s="14"/>
       <c r="L206" s="13"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1">
+    <row r="207" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C207" s="12"/>
       <c r="G207" s="13"/>
       <c r="I207" s="14"/>
       <c r="L207" s="13"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1">
+    <row r="208" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C208" s="12"/>
       <c r="G208" s="13"/>
       <c r="I208" s="14"/>
       <c r="L208" s="13"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1">
+    <row r="209" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C209" s="12"/>
       <c r="G209" s="13"/>
       <c r="I209" s="14"/>
       <c r="L209" s="13"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1">
+    <row r="210" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C210" s="12"/>
       <c r="G210" s="13"/>
       <c r="I210" s="14"/>
       <c r="L210" s="13"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1">
+    <row r="211" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C211" s="12"/>
       <c r="G211" s="13"/>
       <c r="I211" s="14"/>
       <c r="L211" s="13"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1">
+    <row r="212" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C212" s="12"/>
       <c r="G212" s="13"/>
       <c r="I212" s="14"/>
       <c r="L212" s="13"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1">
+    <row r="213" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C213" s="12"/>
       <c r="G213" s="13"/>
       <c r="I213" s="14"/>
       <c r="L213" s="13"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1">
+    <row r="214" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C214" s="12"/>
       <c r="G214" s="13"/>
       <c r="I214" s="14"/>
       <c r="L214" s="13"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1">
+    <row r="215" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C215" s="12"/>
       <c r="G215" s="13"/>
       <c r="I215" s="14"/>
       <c r="L215" s="13"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1">
+    <row r="216" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C216" s="12"/>
       <c r="G216" s="13"/>
       <c r="I216" s="14"/>
       <c r="L216" s="13"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1">
+    <row r="217" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C217" s="12"/>
       <c r="G217" s="13"/>
       <c r="I217" s="14"/>
       <c r="L217" s="13"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1">
+    <row r="218" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C218" s="12"/>
       <c r="G218" s="13"/>
       <c r="I218" s="14"/>
       <c r="L218" s="13"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1">
+    <row r="219" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C219" s="12"/>
       <c r="G219" s="13"/>
       <c r="I219" s="14"/>
       <c r="L219" s="13"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1">
+    <row r="220" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C220" s="12"/>
       <c r="G220" s="13"/>
       <c r="I220" s="14"/>
       <c r="L220" s="13"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1">
+    <row r="221" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C221" s="12"/>
       <c r="G221" s="13"/>
       <c r="I221" s="14"/>
       <c r="L221" s="13"/>
     </row>
-    <row r="222" ht="15.75" customHeight="1">
+    <row r="222" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C222" s="12"/>
       <c r="G222" s="13"/>
       <c r="I222" s="14"/>
       <c r="L222" s="13"/>
     </row>
-    <row r="223" ht="15.75" customHeight="1">
+    <row r="223" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C223" s="12"/>
       <c r="G223" s="13"/>
       <c r="I223" s="14"/>
       <c r="L223" s="13"/>
     </row>
-    <row r="224" ht="15.75" customHeight="1">
+    <row r="224" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C224" s="12"/>
       <c r="G224" s="13"/>
       <c r="I224" s="14"/>
       <c r="L224" s="13"/>
     </row>
-    <row r="225" ht="15.75" customHeight="1">
+    <row r="225" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C225" s="12"/>
       <c r="G225" s="13"/>
       <c r="I225" s="14"/>
       <c r="L225" s="13"/>
     </row>
-    <row r="226" ht="15.75" customHeight="1">
+    <row r="226" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C226" s="12"/>
       <c r="G226" s="13"/>
       <c r="I226" s="14"/>
       <c r="L226" s="13"/>
     </row>
-    <row r="227" ht="15.75" customHeight="1">
+    <row r="227" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C227" s="12"/>
       <c r="G227" s="13"/>
       <c r="I227" s="14"/>
       <c r="L227" s="13"/>
     </row>
-    <row r="228" ht="15.75" customHeight="1">
+    <row r="228" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C228" s="12"/>
       <c r="G228" s="13"/>
       <c r="I228" s="14"/>
       <c r="L228" s="13"/>
     </row>
-    <row r="229" ht="15.75" customHeight="1">
+    <row r="229" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C229" s="12"/>
       <c r="G229" s="13"/>
       <c r="I229" s="14"/>
       <c r="L229" s="13"/>
     </row>
-    <row r="230" ht="15.75" customHeight="1">
+    <row r="230" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C230" s="12"/>
       <c r="G230" s="13"/>
       <c r="I230" s="14"/>
       <c r="L230" s="13"/>
     </row>
-    <row r="231" ht="15.75" customHeight="1">
+    <row r="231" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C231" s="12"/>
       <c r="G231" s="13"/>
       <c r="I231" s="14"/>
       <c r="L231" s="13"/>
     </row>
-    <row r="232" ht="15.75" customHeight="1">
+    <row r="232" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C232" s="12"/>
       <c r="G232" s="13"/>
       <c r="I232" s="14"/>
       <c r="L232" s="13"/>
     </row>
-    <row r="233" ht="15.75" customHeight="1">
+    <row r="233" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C233" s="12"/>
       <c r="G233" s="13"/>
       <c r="I233" s="14"/>
       <c r="L233" s="13"/>
     </row>
-    <row r="234" ht="15.75" customHeight="1">
+    <row r="234" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C234" s="12"/>
       <c r="G234" s="13"/>
       <c r="I234" s="14"/>
       <c r="L234" s="13"/>
     </row>
-    <row r="235" ht="15.75" customHeight="1">
+    <row r="235" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C235" s="12"/>
       <c r="G235" s="13"/>
       <c r="I235" s="14"/>
       <c r="L235" s="13"/>
     </row>
-    <row r="236" ht="15.75" customHeight="1">
+    <row r="236" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C236" s="12"/>
       <c r="G236" s="13"/>
       <c r="I236" s="14"/>
       <c r="L236" s="13"/>
     </row>
-    <row r="237" ht="15.75" customHeight="1">
+    <row r="237" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C237" s="12"/>
       <c r="G237" s="13"/>
       <c r="I237" s="14"/>
       <c r="L237" s="13"/>
     </row>
-    <row r="238" ht="15.75" customHeight="1">
+    <row r="238" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C238" s="12"/>
       <c r="G238" s="13"/>
       <c r="I238" s="14"/>
       <c r="L238" s="13"/>
     </row>
-    <row r="239" ht="15.75" customHeight="1">
+    <row r="239" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C239" s="12"/>
       <c r="G239" s="13"/>
       <c r="I239" s="14"/>
       <c r="L239" s="13"/>
     </row>
-    <row r="240" ht="15.75" customHeight="1">
+    <row r="240" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C240" s="12"/>
       <c r="G240" s="13"/>
       <c r="I240" s="14"/>
       <c r="L240" s="13"/>
     </row>
-    <row r="241" ht="15.75" customHeight="1">
+    <row r="241" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C241" s="12"/>
       <c r="G241" s="13"/>
       <c r="I241" s="14"/>
       <c r="L241" s="13"/>
     </row>
-    <row r="242" ht="15.75" customHeight="1">
+    <row r="242" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C242" s="12"/>
       <c r="G242" s="13"/>
       <c r="I242" s="14"/>
       <c r="L242" s="13"/>
     </row>
-    <row r="243" ht="15.75" customHeight="1">
+    <row r="243" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C243" s="12"/>
       <c r="G243" s="13"/>
       <c r="I243" s="14"/>
       <c r="L243" s="13"/>
     </row>
-    <row r="244" ht="15.75" customHeight="1">
+    <row r="244" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C244" s="12"/>
       <c r="G244" s="13"/>
       <c r="I244" s="14"/>
       <c r="L244" s="13"/>
     </row>
-    <row r="245" ht="15.75" customHeight="1">
+    <row r="245" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C245" s="12"/>
       <c r="G245" s="13"/>
       <c r="I245" s="14"/>
       <c r="L245" s="13"/>
     </row>
-    <row r="246" ht="15.75" customHeight="1">
+    <row r="246" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C246" s="12"/>
       <c r="G246" s="13"/>
       <c r="I246" s="14"/>
       <c r="L246" s="13"/>
     </row>
-    <row r="247" ht="15.75" customHeight="1">
+    <row r="247" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C247" s="12"/>
       <c r="G247" s="13"/>
       <c r="I247" s="14"/>
       <c r="L247" s="13"/>
     </row>
-    <row r="248" ht="15.75" customHeight="1">
+    <row r="248" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C248" s="12"/>
       <c r="G248" s="13"/>
       <c r="I248" s="14"/>
       <c r="L248" s="13"/>
     </row>
-    <row r="249" ht="15.75" customHeight="1">
+    <row r="249" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C249" s="12"/>
       <c r="G249" s="13"/>
       <c r="I249" s="14"/>
       <c r="L249" s="13"/>
     </row>
-    <row r="250" ht="15.75" customHeight="1">
+    <row r="250" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C250" s="12"/>
       <c r="G250" s="13"/>
       <c r="I250" s="14"/>
       <c r="L250" s="13"/>
     </row>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="251" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" spans="3:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>